--- a/public/exports/29189668.xlsx
+++ b/public/exports/29189668.xlsx
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4007231</t>
+          <t xml:space="preserve">372290, 372291</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F4">
-        <v>468</v>
+        <v>2810</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4082383</t>
+          <t xml:space="preserve">372761, 372762</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>370</v>
+        <v>758</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4089548</t>
+          <t xml:space="preserve">372766, 372767</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -290,7 +290,7 @@
         </is>
       </c>
       <c r="F6">
-        <v>2240</v>
+        <v>3260</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100714</t>
+          <t xml:space="preserve">372787, 372788</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F7">
-        <v>2045</v>
+        <v>2948</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4101772</t>
+          <t xml:space="preserve">373331, 373333, 373334, 373335, 373332</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F8">
-        <v>310</v>
+        <v>13536</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110712</t>
+          <t xml:space="preserve">373336, 373337</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>2400</v>
+        <v>4607</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4119181</t>
+          <t xml:space="preserve">374348, 374349, 374350</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>325</v>
+        <v>2959</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">418523, 418524</t>
+          <t xml:space="preserve">374351, 374352</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>5740</v>
+        <v>5406</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609016</t>
+          <t xml:space="preserve">381270</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F12">
-        <v>1797</v>
+        <v>889</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609016</t>
+          <t xml:space="preserve">381882, 381883</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F13">
-        <v>2227</v>
+        <v>1430</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609016</t>
+          <t xml:space="preserve">382839, 382840</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F14">
-        <v>324</v>
+        <v>2298</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609026</t>
+          <t xml:space="preserve">4089548</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="F15">
-        <v>621</v>
+        <v>2240</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609026</t>
+          <t xml:space="preserve">4100714</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F16">
-        <v>264</v>
+        <v>2045</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609026</t>
+          <t xml:space="preserve">4101772</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F17">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609287</t>
+          <t xml:space="preserve">4110712</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F18">
-        <v>743</v>
+        <v>2400</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609292</t>
+          <t xml:space="preserve">414185, 414186</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="F19">
-        <v>4601</v>
+        <v>4582</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609292</t>
+          <t xml:space="preserve">418523, 418524</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>664</v>
+        <v>5740</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610294</t>
+          <t xml:space="preserve">5609016</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F21">
-        <v>826</v>
+        <v>1797</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610294</t>
+          <t xml:space="preserve">5609016</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F22">
-        <v>826</v>
+        <v>2227</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610294</t>
+          <t xml:space="preserve">5609016</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F23">
-        <v>825</v>
+        <v>324</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610294</t>
+          <t xml:space="preserve">5609026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F24">
-        <v>827</v>
+        <v>621</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610294</t>
+          <t xml:space="preserve">5609026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F25">
-        <v>827</v>
+        <v>264</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610294</t>
+          <t xml:space="preserve">5609026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F26">
-        <v>827</v>
+        <v>343</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610294</t>
+          <t xml:space="preserve">5609287</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F27">
-        <v>536</v>
+        <v>743</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5613188</t>
+          <t xml:space="preserve">5609292</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F28">
-        <v>281</v>
+        <v>4601</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5613587</t>
+          <t xml:space="preserve">5609292</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F29">
-        <v>527</v>
+        <v>664</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5615630</t>
+          <t xml:space="preserve">5610294</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F30">
-        <v>588</v>
+        <v>826</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5615630</t>
+          <t xml:space="preserve">5610294</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F31">
-        <v>503</v>
+        <v>826</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">742658, 4110813</t>
+          <t xml:space="preserve">5610294</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F32">
-        <v>2144</v>
+        <v>825</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">742668, 8630451</t>
+          <t xml:space="preserve">5610294</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F33">
-        <v>266</v>
+        <v>827</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">742672, 10108668</t>
+          <t xml:space="preserve">5610294</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F34">
-        <v>280</v>
+        <v>827</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">742675, 9031189</t>
+          <t xml:space="preserve">5610294</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F35">
-        <v>476</v>
+        <v>827</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">742693, 4119308</t>
+          <t xml:space="preserve">5610294</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F36">
-        <v>294</v>
+        <v>536</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">742697, 8674236</t>
+          <t xml:space="preserve">5613188</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F37">
-        <v>733</v>
+        <v>281</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">742710, 4102297</t>
+          <t xml:space="preserve">742675, 9031189</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F38">
-        <v>1572</v>
+        <v>476</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">742714, 4110712</t>
+          <t xml:space="preserve">742693, 4119308</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F39">
-        <v>2480</v>
+        <v>294</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">742725, 5609373</t>
+          <t xml:space="preserve">742697, 8674236</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F40">
-        <v>967</v>
+        <v>733</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">742764, 5615635</t>
+          <t xml:space="preserve">742710, 4102297</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="F41">
-        <v>291</v>
+        <v>1572</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">743536, 4118605</t>
+          <t xml:space="preserve">742714, 4110712</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="F42">
-        <v>264</v>
+        <v>2480</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">743600, 5615631</t>
+          <t xml:space="preserve">742725, 5609373</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="F43">
-        <v>321</v>
+        <v>967</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">743610, 5609374</t>
+          <t xml:space="preserve">742764, 5615635</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F44">
-        <v>1675</v>
+        <v>291</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">743612, 1808945</t>
+          <t xml:space="preserve">743536, 4118605</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F45">
-        <v>407</v>
+        <v>264</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">743613, 1802700</t>
+          <t xml:space="preserve">743600, 5615631</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F46">
-        <v>877</v>
+        <v>321</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">743618, 1508958</t>
+          <t xml:space="preserve">743610, 5609374</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="F47">
-        <v>268</v>
+        <v>1675</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">743638, 8773815</t>
+          <t xml:space="preserve">743612, 1808945</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="F48">
-        <v>3731</v>
+        <v>407</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">743679, 4117867</t>
+          <t xml:space="preserve">743613, 1802700</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F49">
-        <v>355</v>
+        <v>877</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">743680, 4115468</t>
+          <t xml:space="preserve">743638, 8773815</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="F50">
-        <v>256</v>
+        <v>3731</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">743683, 4084282</t>
+          <t xml:space="preserve">743679, 4117867</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="F51">
-        <v>257</v>
+        <v>355</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">743684, 4084750</t>
+          <t xml:space="preserve">743680, 4115468</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="F52">
-        <v>1728</v>
+        <v>256</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">743691, 4086862</t>
+          <t xml:space="preserve">743683, 4084282</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="F53">
-        <v>1322</v>
+        <v>257</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">743691, 4086862</t>
+          <t xml:space="preserve">743684, 4084750</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F54">
-        <v>967</v>
+        <v>1728</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">743692, 10109294</t>
+          <t xml:space="preserve">743691, 4086862</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="F55">
-        <v>2996</v>
+        <v>1322</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,16 +2781,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">743721, 8630451</t>
+          <t xml:space="preserve">743691, 4086862</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F56">
-        <v>470</v>
+        <v>967</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">743729, 4102300</t>
+          <t xml:space="preserve">743692, 10109294</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="F57">
-        <v>2808</v>
+        <v>2996</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2881,16 +2881,16 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">743739, 4117867</t>
+          <t xml:space="preserve">743721, 8630451</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F58">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,16 +2931,16 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7994966</t>
+          <t xml:space="preserve">743729, 4102300</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
-        <v>262</v>
+        <v>2808</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2981,16 +2981,16 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">8552609</t>
+          <t xml:space="preserve">743739, 4117867</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F60">
-        <v>1060</v>
+        <v>481</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3031,16 +3031,16 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8552609</t>
+          <t xml:space="preserve">7994966</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F61">
-        <v>403</v>
+        <v>262</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F62">
-        <v>561</v>
+        <v>1060</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3136,11 +3136,11 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F63">
-        <v>581</v>
+        <v>403</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3181,16 +3181,16 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031189</t>
+          <t xml:space="preserve">8552609</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F64">
-        <v>766</v>
+        <v>561</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031189</t>
+          <t xml:space="preserve">8552609</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F65">
-        <v>2047</v>
+        <v>581</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3286,11 +3286,11 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F66">
-        <v>1969</v>
+        <v>766</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3336,11 +3336,11 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F67">
-        <v>1330</v>
+        <v>2047</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3381,16 +3381,16 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9325670</t>
+          <t xml:space="preserve">9031189</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F68">
-        <v>2191</v>
+        <v>1969</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3431,30 +3431,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">8148470</t>
+          <t xml:space="preserve">9031189</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F69">
-        <v>537</v>
+        <v>1330</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021740</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-01</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3481,30 +3481,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8148470</t>
+          <t xml:space="preserve">9325670</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70">
-        <v>542</v>
+        <v>2191</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021740</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-01</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5613212</t>
+          <t xml:space="preserve">8148470</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F71">
-        <v>286</v>
+        <v>537</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030226</t>
+          <t xml:space="preserve">200021740</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-12</t>
+          <t xml:space="preserve">2019-10-01</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,35 +3581,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4082221</t>
+          <t xml:space="preserve">8148470</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F72">
-        <v>1062</v>
+        <v>542</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215023</t>
+          <t xml:space="preserve">200021740</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2019-10-01</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3631,35 +3631,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4082221</t>
+          <t xml:space="preserve">5613587</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F73">
-        <v>624</v>
+        <v>527</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215043</t>
+          <t xml:space="preserve">200026894</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2020-01-18</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3681,35 +3681,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4082221</t>
+          <t xml:space="preserve">742658, 4110813</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>803</v>
+        <v>2144</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215051</t>
+          <t xml:space="preserve">200045696</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2021-02-16</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3731,35 +3731,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4101772</t>
+          <t xml:space="preserve">742668, 8630451</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F75">
-        <v>9605</v>
+        <v>266</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219450</t>
+          <t xml:space="preserve">200060578</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2022-06-29</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3781,35 +3781,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4101772</t>
+          <t xml:space="preserve">743618, 1508958</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F76">
-        <v>4843</v>
+        <v>268</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219450</t>
+          <t xml:space="preserve">311029231</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2023-12-02</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607555</t>
+          <t xml:space="preserve">4082221</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3840,16 +3840,16 @@
         </is>
       </c>
       <c r="F77">
-        <v>12809</v>
+        <v>1062</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265827</t>
+          <t xml:space="preserve">311215023</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-12</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8642486</t>
+          <t xml:space="preserve">4082221</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F78">
-        <v>5737</v>
+        <v>624</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283179</t>
+          <t xml:space="preserve">311215030</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-09</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8642486</t>
+          <t xml:space="preserve">4082221</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F79">
-        <v>3866</v>
+        <v>803</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283179</t>
+          <t xml:space="preserve">311215030</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-09</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110806</t>
+          <t xml:space="preserve">4101772</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,16 +3990,16 @@
         </is>
       </c>
       <c r="F80">
-        <v>7460</v>
+        <v>9605</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283370</t>
+          <t xml:space="preserve">311219450</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110806</t>
+          <t xml:space="preserve">4101772</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F81">
-        <v>439</v>
+        <v>4843</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283377</t>
+          <t xml:space="preserve">311219450</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4091578</t>
+          <t xml:space="preserve">5607555</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F82">
-        <v>315</v>
+        <v>12809</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283645</t>
+          <t xml:space="preserve">311265827</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-13</t>
+          <t xml:space="preserve">2027-08-12</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4091578</t>
+          <t xml:space="preserve">8642486</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F83">
-        <v>7056</v>
+        <v>5737</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283828</t>
+          <t xml:space="preserve">311283004</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-14</t>
+          <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4091578</t>
+          <t xml:space="preserve">8642486</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F84">
-        <v>336</v>
+        <v>3866</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283828</t>
+          <t xml:space="preserve">311283004</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-14</t>
+          <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4091578</t>
+          <t xml:space="preserve">4110806</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F85">
-        <v>1713</v>
+        <v>7460</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283828</t>
+          <t xml:space="preserve">311283370</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-14</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4109634</t>
+          <t xml:space="preserve">4110806</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F86">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288836</t>
+          <t xml:space="preserve">311283377</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4109634</t>
+          <t xml:space="preserve">4091578</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>385</v>
+        <v>315</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288836</t>
+          <t xml:space="preserve">311283645</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4109634</t>
+          <t xml:space="preserve">4091578</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F88">
-        <v>1092</v>
+        <v>7056</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288836</t>
+          <t xml:space="preserve">311283828</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-11-14</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4109634</t>
+          <t xml:space="preserve">4091578</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F89">
-        <v>758</v>
+        <v>336</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288836</t>
+          <t xml:space="preserve">311283828</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-11-14</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3468104</t>
+          <t xml:space="preserve">4091578</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F90">
-        <v>391</v>
+        <v>1713</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301888</t>
+          <t xml:space="preserve">311283828</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-09</t>
+          <t xml:space="preserve">2027-11-14</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3468335</t>
+          <t xml:space="preserve">4109634</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="F91">
-        <v>497</v>
+        <v>405</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301892</t>
+          <t xml:space="preserve">311288836</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-09</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8244737</t>
+          <t xml:space="preserve">4109634</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F92">
-        <v>495</v>
+        <v>385</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301890</t>
+          <t xml:space="preserve">311288836</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-09</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3469973</t>
+          <t xml:space="preserve">4109634</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F93">
-        <v>7115</v>
+        <v>1092</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311315953</t>
+          <t xml:space="preserve">311288836</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-24</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3469973</t>
+          <t xml:space="preserve">4109634</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F94">
-        <v>2000</v>
+        <v>758</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311315965</t>
+          <t xml:space="preserve">311288836</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-24</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4087268</t>
+          <t xml:space="preserve">3468104</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4740,16 +4740,16 @@
         </is>
       </c>
       <c r="F95">
-        <v>447</v>
+        <v>391</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311318981</t>
+          <t xml:space="preserve">311301888</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-07</t>
+          <t xml:space="preserve">2028-03-09</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4087268</t>
+          <t xml:space="preserve">3468335</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F96">
-        <v>2448</v>
+        <v>497</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311318981</t>
+          <t xml:space="preserve">311301892</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-07</t>
+          <t xml:space="preserve">2028-03-09</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4087268</t>
+          <t xml:space="preserve">8244737</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F97">
-        <v>255</v>
+        <v>495</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311318982</t>
+          <t xml:space="preserve">311301890</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-07</t>
+          <t xml:space="preserve">2028-03-09</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4086352</t>
+          <t xml:space="preserve">3469973</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4890,16 +4890,16 @@
         </is>
       </c>
       <c r="F98">
-        <v>1441</v>
+        <v>7115</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319711</t>
+          <t xml:space="preserve">311315953</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-11</t>
+          <t xml:space="preserve">2028-05-24</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4086352</t>
+          <t xml:space="preserve">3469973</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F99">
-        <v>965</v>
+        <v>2000</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319711</t>
+          <t xml:space="preserve">311315965</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-11</t>
+          <t xml:space="preserve">2028-05-24</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4086352</t>
+          <t xml:space="preserve">4087268</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F100">
-        <v>3943</v>
+        <v>447</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319711</t>
+          <t xml:space="preserve">311318981</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-11</t>
+          <t xml:space="preserve">2028-06-07</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4086352</t>
+          <t xml:space="preserve">4087268</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F101">
-        <v>330</v>
+        <v>2448</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319711</t>
+          <t xml:space="preserve">311318981</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-11</t>
+          <t xml:space="preserve">2028-06-07</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4086352</t>
+          <t xml:space="preserve">4087268</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F102">
-        <v>1573</v>
+        <v>255</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319711</t>
+          <t xml:space="preserve">311318982</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-11</t>
+          <t xml:space="preserve">2028-06-07</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5136,11 +5136,11 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F103">
-        <v>499</v>
+        <v>1441</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7812193</t>
+          <t xml:space="preserve">4086352</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F104">
-        <v>5919</v>
+        <v>965</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320059</t>
+          <t xml:space="preserve">311319711</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-12</t>
+          <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7812193</t>
+          <t xml:space="preserve">4086352</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="F105">
-        <v>1551</v>
+        <v>3943</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320059</t>
+          <t xml:space="preserve">311319711</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-12</t>
+          <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4109306</t>
+          <t xml:space="preserve">4086352</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F106">
-        <v>5398</v>
+        <v>330</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320269</t>
+          <t xml:space="preserve">311319711</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-13</t>
+          <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4109306</t>
+          <t xml:space="preserve">4086352</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F107">
-        <v>895</v>
+        <v>1573</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320269</t>
+          <t xml:space="preserve">311319711</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-13</t>
+          <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4109306</t>
+          <t xml:space="preserve">4086352</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F108">
-        <v>425</v>
+        <v>499</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320269</t>
+          <t xml:space="preserve">311319711</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-13</t>
+          <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,25 +5431,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4109306</t>
+          <t xml:space="preserve">7812193</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F109">
-        <v>403</v>
+        <v>5919</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320269</t>
+          <t xml:space="preserve">311320059</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-13</t>
+          <t xml:space="preserve">2028-06-12</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031310</t>
+          <t xml:space="preserve">7812193</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F110">
-        <v>4009</v>
+        <v>1551</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321113</t>
+          <t xml:space="preserve">311320059</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-18</t>
+          <t xml:space="preserve">2028-06-12</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,25 +5531,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031310</t>
+          <t xml:space="preserve">4109306</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F111">
-        <v>1394</v>
+        <v>5398</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321113</t>
+          <t xml:space="preserve">311320269</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-18</t>
+          <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,25 +5581,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4007498</t>
+          <t xml:space="preserve">4109306</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F112">
-        <v>10878</v>
+        <v>895</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323459</t>
+          <t xml:space="preserve">311320269</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-28</t>
+          <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4007498</t>
+          <t xml:space="preserve">4109306</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F113">
-        <v>568</v>
+        <v>425</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323459</t>
+          <t xml:space="preserve">311320269</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-28</t>
+          <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4007498</t>
+          <t xml:space="preserve">4109306</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="F114">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323459</t>
+          <t xml:space="preserve">311320269</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-28</t>
+          <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8211414</t>
+          <t xml:space="preserve">9031310</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="F115">
-        <v>1088</v>
+        <v>4009</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324268</t>
+          <t xml:space="preserve">311321113</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-06-18</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8211414</t>
+          <t xml:space="preserve">9031310</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F116">
-        <v>254</v>
+        <v>1394</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324269</t>
+          <t xml:space="preserve">311321113</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-06-18</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8211414</t>
+          <t xml:space="preserve">4007498</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F117">
-        <v>386</v>
+        <v>10878</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324269</t>
+          <t xml:space="preserve">311323459</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8211414</t>
+          <t xml:space="preserve">4007498</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F118">
-        <v>801</v>
+        <v>568</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324268</t>
+          <t xml:space="preserve">311323459</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8211414</t>
+          <t xml:space="preserve">4007498</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F119">
-        <v>1088</v>
+        <v>396</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324268</t>
+          <t xml:space="preserve">311323459</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5986,11 +5986,11 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120">
-        <v>392</v>
+        <v>1088</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6036,15 +6036,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F121">
-        <v>593</v>
+        <v>254</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324268</t>
+          <t xml:space="preserve">311324269</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6086,15 +6086,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F122">
-        <v>1645</v>
+        <v>386</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324268</t>
+          <t xml:space="preserve">311324269</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6136,11 +6136,11 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F123">
-        <v>1530</v>
+        <v>801</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6181,25 +6181,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5616102</t>
+          <t xml:space="preserve">8211414</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F124">
-        <v>13413</v>
+        <v>1088</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324575</t>
+          <t xml:space="preserve">311324268</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-04</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4084722</t>
+          <t xml:space="preserve">8211414</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F125">
-        <v>1955</v>
+        <v>392</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330753</t>
+          <t xml:space="preserve">311324268</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-16</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4087573</t>
+          <t xml:space="preserve">8211414</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F126">
-        <v>946</v>
+        <v>593</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311332433</t>
+          <t xml:space="preserve">311324268</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-24</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,25 +6331,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4087933</t>
+          <t xml:space="preserve">8211414</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F127">
-        <v>365</v>
+        <v>1645</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311332424</t>
+          <t xml:space="preserve">311324268</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-24</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4088005</t>
+          <t xml:space="preserve">8211414</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F128">
-        <v>2097</v>
+        <v>1530</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311332438</t>
+          <t xml:space="preserve">311324268</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-24</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5614837</t>
+          <t xml:space="preserve">5616102</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6440,16 +6440,16 @@
         </is>
       </c>
       <c r="F129">
-        <v>11721</v>
+        <v>13413</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311333416</t>
+          <t xml:space="preserve">311324558</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-30</t>
+          <t xml:space="preserve">2028-07-04</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5611242</t>
+          <t xml:space="preserve">4084722</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F130">
-        <v>930</v>
+        <v>1955</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311333946</t>
+          <t xml:space="preserve">311330753</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-03</t>
+          <t xml:space="preserve">2028-08-16</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">7188494</t>
+          <t xml:space="preserve">4087573</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="F131">
-        <v>693</v>
+        <v>946</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311334488</t>
+          <t xml:space="preserve">311332433</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-05</t>
+          <t xml:space="preserve">2028-08-24</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5608310</t>
+          <t xml:space="preserve">4087933</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="F132">
-        <v>559</v>
+        <v>365</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311337037</t>
+          <t xml:space="preserve">311332424</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-19</t>
+          <t xml:space="preserve">2028-08-24</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5608323</t>
+          <t xml:space="preserve">4088005</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6640,16 +6640,16 @@
         </is>
       </c>
       <c r="F133">
-        <v>372</v>
+        <v>2097</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311338328</t>
+          <t xml:space="preserve">311332438</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-26</t>
+          <t xml:space="preserve">2028-08-24</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">381270</t>
+          <t xml:space="preserve">5614837</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,16 +6690,16 @@
         </is>
       </c>
       <c r="F134">
-        <v>889</v>
+        <v>11721</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340779</t>
+          <t xml:space="preserve">311333416</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-10</t>
+          <t xml:space="preserve">2028-08-30</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">10191959</t>
+          <t xml:space="preserve">7188494</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6740,16 +6740,16 @@
         </is>
       </c>
       <c r="F135">
-        <v>920</v>
+        <v>693</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311341759</t>
+          <t xml:space="preserve">311334488</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-16</t>
+          <t xml:space="preserve">2028-09-05</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9686576</t>
+          <t xml:space="preserve">5611242</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F136">
-        <v>1020</v>
+        <v>930</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311341760</t>
+          <t xml:space="preserve">311334833</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-16</t>
+          <t xml:space="preserve">2028-09-07</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">4087245</t>
+          <t xml:space="preserve">5608310</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6840,16 +6840,16 @@
         </is>
       </c>
       <c r="F137">
-        <v>265</v>
+        <v>559</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311343092</t>
+          <t xml:space="preserve">311337033</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-24</t>
+          <t xml:space="preserve">2028-09-19</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4087247</t>
+          <t xml:space="preserve">5608323</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="F138">
-        <v>596</v>
+        <v>372</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311343112</t>
+          <t xml:space="preserve">311338328</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-24</t>
+          <t xml:space="preserve">2028-09-26</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">372761, 372762</t>
+          <t xml:space="preserve">10191959</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6940,16 +6940,16 @@
         </is>
       </c>
       <c r="F139">
-        <v>758</v>
+        <v>920</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311343448</t>
+          <t xml:space="preserve">311341759</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-26</t>
+          <t xml:space="preserve">2028-10-16</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">9209497</t>
+          <t xml:space="preserve">9686576</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F140">
-        <v>722</v>
+        <v>1020</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311343535</t>
+          <t xml:space="preserve">311341760</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-26</t>
+          <t xml:space="preserve">2028-10-16</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9209497</t>
+          <t xml:space="preserve">4087245</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F141">
-        <v>722</v>
+        <v>265</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311343535</t>
+          <t xml:space="preserve">311343092</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-26</t>
+          <t xml:space="preserve">2028-10-24</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9209497</t>
+          <t xml:space="preserve">4087247</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F142">
-        <v>1468</v>
+        <v>596</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311343550</t>
+          <t xml:space="preserve">311343112</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-26</t>
+          <t xml:space="preserve">2028-10-24</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F143">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F144">
@@ -7231,25 +7231,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9256087</t>
+          <t xml:space="preserve">9209497</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F145">
-        <v>1199</v>
+        <v>1468</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311343841</t>
+          <t xml:space="preserve">311343550</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-29</t>
+          <t xml:space="preserve">2028-10-26</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8280030</t>
+          <t xml:space="preserve">9209497</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F146">
-        <v>255</v>
+        <v>722</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311344152</t>
+          <t xml:space="preserve">311343535</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-30</t>
+          <t xml:space="preserve">2028-10-26</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,25 +7331,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4087071</t>
+          <t xml:space="preserve">9209497</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F147">
-        <v>455</v>
+        <v>722</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311345033</t>
+          <t xml:space="preserve">311343535</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-05</t>
+          <t xml:space="preserve">2028-10-26</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5613257</t>
+          <t xml:space="preserve">9256087</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7390,16 +7390,16 @@
         </is>
       </c>
       <c r="F148">
-        <v>1588</v>
+        <v>1199</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311345782</t>
+          <t xml:space="preserve">311343841</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-08</t>
+          <t xml:space="preserve">2028-10-29</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808939</t>
+          <t xml:space="preserve">8280030</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F149">
-        <v>586</v>
+        <v>255</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346456</t>
+          <t xml:space="preserve">311344152</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-13</t>
+          <t xml:space="preserve">2028-10-30</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808940</t>
+          <t xml:space="preserve">4087071</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="F150">
-        <v>1709</v>
+        <v>455</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346554</t>
+          <t xml:space="preserve">311345033</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-13</t>
+          <t xml:space="preserve">2028-11-05</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4115802</t>
+          <t xml:space="preserve">5613257</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7540,16 +7540,16 @@
         </is>
       </c>
       <c r="F151">
-        <v>469</v>
+        <v>1588</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347908</t>
+          <t xml:space="preserve">311345782</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-21</t>
+          <t xml:space="preserve">2028-11-08</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4087239</t>
+          <t xml:space="preserve">1808939</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F152">
-        <v>2791</v>
+        <v>586</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348100</t>
+          <t xml:space="preserve">311346456</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-22</t>
+          <t xml:space="preserve">2028-11-13</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607629</t>
+          <t xml:space="preserve">1808940</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F153">
-        <v>976</v>
+        <v>1709</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348230</t>
+          <t xml:space="preserve">311346554</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-22</t>
+          <t xml:space="preserve">2028-11-13</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607629</t>
+          <t xml:space="preserve">4115802</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F154">
-        <v>2096</v>
+        <v>469</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348230</t>
+          <t xml:space="preserve">311347908</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-22</t>
+          <t xml:space="preserve">2028-11-21</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">7186920</t>
+          <t xml:space="preserve">4087239</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -7740,11 +7740,11 @@
         </is>
       </c>
       <c r="F155">
-        <v>18615</v>
+        <v>2791</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348185</t>
+          <t xml:space="preserve">311348100</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7781,20 +7781,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">7186920</t>
+          <t xml:space="preserve">5607629</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F156">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348185</t>
+          <t xml:space="preserve">311348230</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7831,20 +7831,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">7186920</t>
+          <t xml:space="preserve">5607629</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F157">
-        <v>376</v>
+        <v>2096</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348185</t>
+          <t xml:space="preserve">311348230</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7886,15 +7886,15 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F158">
-        <v>1272</v>
+        <v>18615</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348184</t>
+          <t xml:space="preserve">311348185</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8642473</t>
+          <t xml:space="preserve">7186920</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="F159">
-        <v>801</v>
+        <v>984</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348373</t>
+          <t xml:space="preserve">311348185</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-23</t>
+          <t xml:space="preserve">2028-11-22</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8642473</t>
+          <t xml:space="preserve">7186920</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F160">
-        <v>337</v>
+        <v>376</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348373</t>
+          <t xml:space="preserve">311348185</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-23</t>
+          <t xml:space="preserve">2028-11-22</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5608042</t>
+          <t xml:space="preserve">7186920</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F161">
-        <v>371</v>
+        <v>1272</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348751</t>
+          <t xml:space="preserve">311348184</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-27</t>
+          <t xml:space="preserve">2028-11-22</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5608042</t>
+          <t xml:space="preserve">8642473</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="F162">
-        <v>1374</v>
+        <v>801</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348747</t>
+          <t xml:space="preserve">311348373</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-27</t>
+          <t xml:space="preserve">2028-11-23</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607403</t>
+          <t xml:space="preserve">8642473</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F163">
-        <v>288</v>
+        <v>337</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350092</t>
+          <t xml:space="preserve">311348373</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-05</t>
+          <t xml:space="preserve">2028-11-23</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8003990</t>
+          <t xml:space="preserve">5608042</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8190,16 +8190,16 @@
         </is>
       </c>
       <c r="F164">
-        <v>732</v>
+        <v>371</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350077</t>
+          <t xml:space="preserve">311348751</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-05</t>
+          <t xml:space="preserve">2028-11-27</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">372766, 372767</t>
+          <t xml:space="preserve">5608042</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F165">
-        <v>3260</v>
+        <v>1374</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311351592</t>
+          <t xml:space="preserve">311348747</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-14</t>
+          <t xml:space="preserve">2028-11-27</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110085</t>
+          <t xml:space="preserve">5607403</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8290,16 +8290,16 @@
         </is>
       </c>
       <c r="F166">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352640</t>
+          <t xml:space="preserve">311350092</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-20</t>
+          <t xml:space="preserve">2028-12-05</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">372290, 372291</t>
+          <t xml:space="preserve">8003990</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8340,16 +8340,16 @@
         </is>
       </c>
       <c r="F167">
-        <v>2810</v>
+        <v>732</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352881</t>
+          <t xml:space="preserve">311350077</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-21</t>
+          <t xml:space="preserve">2028-12-05</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730947</t>
+          <t xml:space="preserve">4110085</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F168">
-        <v>683</v>
+        <v>260</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353743</t>
+          <t xml:space="preserve">311352640</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-08</t>
+          <t xml:space="preserve">2028-12-20</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">8205038</t>
+          <t xml:space="preserve">7730947</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8440,16 +8440,16 @@
         </is>
       </c>
       <c r="F169">
-        <v>708</v>
+        <v>683</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354539</t>
+          <t xml:space="preserve">311353743</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-14</t>
+          <t xml:space="preserve">2029-01-08</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">373331, 373333, 373334, 373335, 373332</t>
+          <t xml:space="preserve">8205038</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F170">
-        <v>13536</v>
+        <v>708</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354854</t>
+          <t xml:space="preserve">311354539</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-16</t>
+          <t xml:space="preserve">2029-01-14</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">373336, 373337</t>
+          <t xml:space="preserve">5614905</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -8540,11 +8540,11 @@
         </is>
       </c>
       <c r="F171">
-        <v>4607</v>
+        <v>912</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354859</t>
+          <t xml:space="preserve">311354865</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5614905</t>
+          <t xml:space="preserve">5614947</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8590,11 +8590,11 @@
         </is>
       </c>
       <c r="F172">
-        <v>912</v>
+        <v>327</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354865</t>
+          <t xml:space="preserve">311354863</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5614947</t>
+          <t xml:space="preserve">4110353</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8640,16 +8640,16 @@
         </is>
       </c>
       <c r="F173">
-        <v>327</v>
+        <v>2096</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354863</t>
+          <t xml:space="preserve">311356902</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-16</t>
+          <t xml:space="preserve">2029-01-29</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110353</t>
+          <t xml:space="preserve">7730945</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8690,11 +8690,11 @@
         </is>
       </c>
       <c r="F174">
-        <v>2096</v>
+        <v>403</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356902</t>
+          <t xml:space="preserve">311356905</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8731,25 +8731,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730945</t>
+          <t xml:space="preserve">4101916</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F175">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356905</t>
+          <t xml:space="preserve">311357215</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-29</t>
+          <t xml:space="preserve">2029-01-30</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,20 +8781,20 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4101916</t>
+          <t xml:space="preserve">9755387</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F176">
-        <v>413</v>
+        <v>1056</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311357215</t>
+          <t xml:space="preserve">311357231</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9755387</t>
+          <t xml:space="preserve">4109548</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -8840,16 +8840,16 @@
         </is>
       </c>
       <c r="F177">
-        <v>1056</v>
+        <v>353</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311357231</t>
+          <t xml:space="preserve">311357836</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-30</t>
+          <t xml:space="preserve">2029-02-04</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4109548</t>
+          <t xml:space="preserve">5615193</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8890,16 +8890,16 @@
         </is>
       </c>
       <c r="F178">
-        <v>353</v>
+        <v>4460</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311357836</t>
+          <t xml:space="preserve">311359453</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-04</t>
+          <t xml:space="preserve">2029-02-13</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8936,11 +8936,11 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F179">
-        <v>4460</v>
+        <v>1719</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5615193</t>
+          <t xml:space="preserve">4109116</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F180">
-        <v>1719</v>
+        <v>337</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311359453</t>
+          <t xml:space="preserve">311360037</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-13</t>
+          <t xml:space="preserve">2029-02-18</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4109116</t>
+          <t xml:space="preserve">1443814</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F181">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360037</t>
+          <t xml:space="preserve">311362524</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-18</t>
+          <t xml:space="preserve">2029-03-04</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1443814</t>
+          <t xml:space="preserve">8396316</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F182">
-        <v>334</v>
+        <v>504</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311362525</t>
+          <t xml:space="preserve">311363877</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-04</t>
+          <t xml:space="preserve">2029-03-11</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8396316</t>
+          <t xml:space="preserve">8773818</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -9140,16 +9140,16 @@
         </is>
       </c>
       <c r="F183">
-        <v>504</v>
+        <v>545</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311363877</t>
+          <t xml:space="preserve">311365178</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-11</t>
+          <t xml:space="preserve">2029-03-18</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">8773818</t>
+          <t xml:space="preserve">100006462</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F184">
-        <v>545</v>
+        <v>1745</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365178</t>
+          <t xml:space="preserve">311365899</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-18</t>
+          <t xml:space="preserve">2029-03-20</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,25 +9231,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">100006462</t>
+          <t xml:space="preserve">4007231</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F185">
-        <v>1745</v>
+        <v>468</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365899</t>
+          <t xml:space="preserve">311368380</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-20</t>
+          <t xml:space="preserve">2029-04-01</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381363</t>
+          <t xml:space="preserve">311383184</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-07</t>
+          <t xml:space="preserve">2029-06-18</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10044,12 +10044,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382871</t>
+          <t xml:space="preserve">311383184</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2029-06-18</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">372787, 372788</t>
+          <t xml:space="preserve">4112531</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -10390,16 +10390,16 @@
         </is>
       </c>
       <c r="F208">
-        <v>2948</v>
+        <v>351</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311387243</t>
+          <t xml:space="preserve">311390735</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-05</t>
+          <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">381882, 381883</t>
+          <t xml:space="preserve">5607904</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -10440,16 +10440,16 @@
         </is>
       </c>
       <c r="F209">
-        <v>1430</v>
+        <v>3070</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390589</t>
+          <t xml:space="preserve">311392596</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-30</t>
+          <t xml:space="preserve">2029-08-13</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">7235664</t>
+          <t xml:space="preserve">5614832</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -10490,16 +10490,16 @@
         </is>
       </c>
       <c r="F210">
-        <v>358</v>
+        <v>281</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390646</t>
+          <t xml:space="preserve">311392891</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-30</t>
+          <t xml:space="preserve">2029-08-14</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112531</t>
+          <t xml:space="preserve">4108607</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -10540,16 +10540,16 @@
         </is>
       </c>
       <c r="F211">
-        <v>351</v>
+        <v>1503</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390735</t>
+          <t xml:space="preserve">311393052</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-31</t>
+          <t xml:space="preserve">2029-08-15</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,25 +10581,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607904</t>
+          <t xml:space="preserve">8674003</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F212">
-        <v>3070</v>
+        <v>1898</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311392596</t>
+          <t xml:space="preserve">311392997</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-13</t>
+          <t xml:space="preserve">2029-08-15</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5614832</t>
+          <t xml:space="preserve">8865608</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -10640,16 +10640,16 @@
         </is>
       </c>
       <c r="F213">
-        <v>281</v>
+        <v>456</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311392891</t>
+          <t xml:space="preserve">311393122</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-14</t>
+          <t xml:space="preserve">2029-08-15</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10681,25 +10681,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">4108607</t>
+          <t xml:space="preserve">5613212</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F214">
-        <v>1503</v>
+        <v>286</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311393052</t>
+          <t xml:space="preserve">311393687</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-15</t>
+          <t xml:space="preserve">2029-08-19</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">8674003</t>
+          <t xml:space="preserve">5613212</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -10740,16 +10740,16 @@
         </is>
       </c>
       <c r="F215">
-        <v>1898</v>
+        <v>656</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311392997</t>
+          <t xml:space="preserve">311393677</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-15</t>
+          <t xml:space="preserve">2029-08-19</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8865608</t>
+          <t xml:space="preserve">5612459</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -10790,16 +10790,16 @@
         </is>
       </c>
       <c r="F216">
-        <v>456</v>
+        <v>1507</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311393122</t>
+          <t xml:space="preserve">311394251</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-15</t>
+          <t xml:space="preserve">2029-08-21</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10831,25 +10831,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5613212</t>
+          <t xml:space="preserve">5614649</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F217">
-        <v>656</v>
+        <v>569</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311393677</t>
+          <t xml:space="preserve">311395717</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-19</t>
+          <t xml:space="preserve">2029-08-29</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,25 +10881,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5612459</t>
+          <t xml:space="preserve">5614649</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F218">
-        <v>1507</v>
+        <v>836</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311394251</t>
+          <t xml:space="preserve">311395717</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-21</t>
+          <t xml:space="preserve">2029-08-29</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10936,15 +10936,15 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F219">
-        <v>569</v>
+        <v>415</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395717</t>
+          <t xml:space="preserve">311395718</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10986,11 +10986,11 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F220">
-        <v>836</v>
+        <v>640</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -11031,20 +11031,20 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5614649</t>
+          <t xml:space="preserve">9292220</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F221">
-        <v>415</v>
+        <v>5636</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395718</t>
+          <t xml:space="preserve">311395613</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5614649</t>
+          <t xml:space="preserve">5609705</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F222">
-        <v>640</v>
+        <v>377</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395717</t>
+          <t xml:space="preserve">311396090</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-29</t>
+          <t xml:space="preserve">2029-09-03</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -11131,25 +11131,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">9292220</t>
+          <t xml:space="preserve">5609705</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F223">
-        <v>5636</v>
+        <v>394</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395613</t>
+          <t xml:space="preserve">311396090</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-29</t>
+          <t xml:space="preserve">2029-09-03</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">414185, 414186</t>
+          <t xml:space="preserve">5615482</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -11190,16 +11190,16 @@
         </is>
       </c>
       <c r="F224">
-        <v>4582</v>
+        <v>518</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311396093</t>
+          <t xml:space="preserve">311396754</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-03</t>
+          <t xml:space="preserve">2029-09-05</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609705</t>
+          <t xml:space="preserve">8190479</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -11240,16 +11240,16 @@
         </is>
       </c>
       <c r="F225">
-        <v>377</v>
+        <v>688</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311396090</t>
+          <t xml:space="preserve">311396751</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-03</t>
+          <t xml:space="preserve">2029-09-05</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -11281,25 +11281,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609705</t>
+          <t xml:space="preserve">9187583</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F226">
-        <v>394</v>
+        <v>528</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311396090</t>
+          <t xml:space="preserve">311398812</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-03</t>
+          <t xml:space="preserve">2029-09-17</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5615482</t>
+          <t xml:space="preserve">9187583</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -11340,16 +11340,16 @@
         </is>
       </c>
       <c r="F227">
-        <v>518</v>
+        <v>2283</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311396754</t>
+          <t xml:space="preserve">311399897</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-05</t>
+          <t xml:space="preserve">2029-09-23</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">8190479</t>
+          <t xml:space="preserve">10194651</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -11390,16 +11390,16 @@
         </is>
       </c>
       <c r="F228">
-        <v>688</v>
+        <v>5493</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311396751</t>
+          <t xml:space="preserve">311400636</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-05</t>
+          <t xml:space="preserve">2029-09-26</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11431,25 +11431,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9187583</t>
+          <t xml:space="preserve">10194651</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F229">
-        <v>528</v>
+        <v>864</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311398812</t>
+          <t xml:space="preserve">311400636</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-17</t>
+          <t xml:space="preserve">2029-09-26</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">9187583</t>
+          <t xml:space="preserve">9927941</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -11490,16 +11490,16 @@
         </is>
       </c>
       <c r="F230">
-        <v>2283</v>
+        <v>923</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311399897</t>
+          <t xml:space="preserve">311400640</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-23</t>
+          <t xml:space="preserve">2029-09-26</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">10194651</t>
+          <t xml:space="preserve">100020177</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -11540,16 +11540,16 @@
         </is>
       </c>
       <c r="F231">
-        <v>5493</v>
+        <v>1159</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311400636</t>
+          <t xml:space="preserve">311401110</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-26</t>
+          <t xml:space="preserve">2029-09-30</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11581,25 +11581,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">10194651</t>
+          <t xml:space="preserve">100020177</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F232">
-        <v>864</v>
+        <v>1057</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311400636</t>
+          <t xml:space="preserve">311401110</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-26</t>
+          <t xml:space="preserve">2029-09-30</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11631,25 +11631,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">9927941</t>
+          <t xml:space="preserve">100020177</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F233">
-        <v>923</v>
+        <v>1165</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311400640</t>
+          <t xml:space="preserve">311401110</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-26</t>
+          <t xml:space="preserve">2029-09-30</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11686,11 +11686,11 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F234">
-        <v>1159</v>
+        <v>584</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">100020177</t>
+          <t xml:space="preserve">9187583</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -11740,16 +11740,16 @@
         </is>
       </c>
       <c r="F235">
-        <v>1057</v>
+        <v>2708</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311401110</t>
+          <t xml:space="preserve">311401278</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-30</t>
+          <t xml:space="preserve">2029-10-01</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11781,25 +11781,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">100020177</t>
+          <t xml:space="preserve">1446054</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F236">
-        <v>1165</v>
+        <v>862</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311401110</t>
+          <t xml:space="preserve">311401797</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-30</t>
+          <t xml:space="preserve">2029-10-03</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11831,25 +11831,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">100020177</t>
+          <t xml:space="preserve">5607942</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F237">
-        <v>584</v>
+        <v>3467</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311401110</t>
+          <t xml:space="preserve">311402521</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-30</t>
+          <t xml:space="preserve">2029-10-08</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11881,25 +11881,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">9187583</t>
+          <t xml:space="preserve">5612926</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F238">
-        <v>2708</v>
+        <v>333</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311401278</t>
+          <t xml:space="preserve">311402523</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-01</t>
+          <t xml:space="preserve">2029-10-08</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446054</t>
+          <t xml:space="preserve">5607999</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -11940,16 +11940,16 @@
         </is>
       </c>
       <c r="F239">
-        <v>862</v>
+        <v>1407</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311401797</t>
+          <t xml:space="preserve">311406164</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-03</t>
+          <t xml:space="preserve">2029-10-29</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11981,25 +11981,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607942</t>
+          <t xml:space="preserve">5607999</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F240">
-        <v>3467</v>
+        <v>300</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402521</t>
+          <t xml:space="preserve">311406165</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-08</t>
+          <t xml:space="preserve">2029-10-29</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5612926</t>
+          <t xml:space="preserve">7185909</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -12040,16 +12040,16 @@
         </is>
       </c>
       <c r="F241">
-        <v>333</v>
+        <v>7267</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402523</t>
+          <t xml:space="preserve">311407285</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-08</t>
+          <t xml:space="preserve">2029-11-05</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -12081,25 +12081,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607999</t>
+          <t xml:space="preserve">4119181</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F242">
-        <v>1407</v>
+        <v>325</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311406164</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-29</t>
+          <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -12131,25 +12131,25 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607999</t>
+          <t xml:space="preserve">7968635</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F243">
-        <v>300</v>
+        <v>766</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311406165</t>
+          <t xml:space="preserve">311409143</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-29</t>
+          <t xml:space="preserve">2029-11-15</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">7185909</t>
+          <t xml:space="preserve">4007476</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -12190,16 +12190,16 @@
         </is>
       </c>
       <c r="F244">
-        <v>7267</v>
+        <v>690</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407285</t>
+          <t xml:space="preserve">311410294</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-05</t>
+          <t xml:space="preserve">2029-11-22</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -12231,25 +12231,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">7968635</t>
+          <t xml:space="preserve">4007476</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F245">
-        <v>766</v>
+        <v>690</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311409143</t>
+          <t xml:space="preserve">311410294</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-15</t>
+          <t xml:space="preserve">2029-11-22</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -12286,11 +12286,11 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F246">
-        <v>690</v>
+        <v>1247</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -12336,11 +12336,11 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F247">
-        <v>690</v>
+        <v>1356</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -12386,11 +12386,11 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F248">
-        <v>1247</v>
+        <v>1182</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -12431,25 +12431,25 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">4007476</t>
+          <t xml:space="preserve">4101369</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F249">
-        <v>1356</v>
+        <v>388</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410294</t>
+          <t xml:space="preserve">311410597</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-22</t>
+          <t xml:space="preserve">2029-11-25</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -12481,25 +12481,25 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">4007476</t>
+          <t xml:space="preserve">5607904</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F250">
-        <v>1182</v>
+        <v>862</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410294</t>
+          <t xml:space="preserve">311412167</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-22</t>
+          <t xml:space="preserve">2029-12-04</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">4101369</t>
+          <t xml:space="preserve">1808944</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -12540,16 +12540,16 @@
         </is>
       </c>
       <c r="F251">
-        <v>388</v>
+        <v>627</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410597</t>
+          <t xml:space="preserve">311412880</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-25</t>
+          <t xml:space="preserve">2029-12-09</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -12581,25 +12581,25 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607904</t>
+          <t xml:space="preserve">5609367</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F252">
-        <v>862</v>
+        <v>441</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311412167</t>
+          <t xml:space="preserve">311413398</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-04</t>
+          <t xml:space="preserve">2029-12-11</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808944</t>
+          <t xml:space="preserve">3469336</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -12640,16 +12640,16 @@
         </is>
       </c>
       <c r="F253">
-        <v>627</v>
+        <v>734</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311412880</t>
+          <t xml:space="preserve">311414021</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-09</t>
+          <t xml:space="preserve">2029-12-16</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -12681,25 +12681,25 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">374348, 374349, 374350</t>
+          <t xml:space="preserve">5609423</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F254">
-        <v>2959</v>
+        <v>4290</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311413114</t>
+          <t xml:space="preserve">311416384</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-10</t>
+          <t xml:space="preserve">2030-01-09</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609367</t>
+          <t xml:space="preserve">5610040</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -12740,16 +12740,16 @@
         </is>
       </c>
       <c r="F255">
-        <v>441</v>
+        <v>1150</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311413398</t>
+          <t xml:space="preserve">311416974</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-11</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -12781,25 +12781,25 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">3469336</t>
+          <t xml:space="preserve">5610040</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F256">
-        <v>734</v>
+        <v>2876</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311414021</t>
+          <t xml:space="preserve">311416974</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-16</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -12831,25 +12831,25 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">374351, 374352</t>
+          <t xml:space="preserve">5610040</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F257">
-        <v>5406</v>
+        <v>268</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311414081</t>
+          <t xml:space="preserve">311416975</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-16</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -12881,25 +12881,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609423</t>
+          <t xml:space="preserve">5610040</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F258">
-        <v>4290</v>
+        <v>268</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416384</t>
+          <t xml:space="preserve">311416975</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-09</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -12936,15 +12936,15 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F259">
-        <v>1150</v>
+        <v>268</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416974</t>
+          <t xml:space="preserve">311416975</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -12986,15 +12986,15 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F260">
-        <v>2876</v>
+        <v>268</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416974</t>
+          <t xml:space="preserve">311416975</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -13031,25 +13031,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610040</t>
+          <t xml:space="preserve">5609375</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F261">
-        <v>268</v>
+        <v>502</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416975</t>
+          <t xml:space="preserve">311418052</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-01-20</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -13081,25 +13081,25 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610040</t>
+          <t xml:space="preserve">8019803</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F262">
-        <v>268</v>
+        <v>717</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416975</t>
+          <t xml:space="preserve">311418306</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-01-21</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -13131,25 +13131,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610040</t>
+          <t xml:space="preserve">5609372</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F263">
-        <v>268</v>
+        <v>478</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416975</t>
+          <t xml:space="preserve">311418590</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-01-23</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -13181,25 +13181,25 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610040</t>
+          <t xml:space="preserve">4101367</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F264">
-        <v>268</v>
+        <v>1635</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416975</t>
+          <t xml:space="preserve">311418870</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-01-24</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -13231,25 +13231,25 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609375</t>
+          <t xml:space="preserve">5615630</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F265">
-        <v>502</v>
+        <v>1463</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418052</t>
+          <t xml:space="preserve">311420970</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-20</t>
+          <t xml:space="preserve">2030-02-05</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -13281,25 +13281,25 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">8019803</t>
+          <t xml:space="preserve">5615630</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F266">
-        <v>717</v>
+        <v>588</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418306</t>
+          <t xml:space="preserve">311420979</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-21</t>
+          <t xml:space="preserve">2030-02-05</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -13331,25 +13331,25 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609372</t>
+          <t xml:space="preserve">5615630</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F267">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418590</t>
+          <t xml:space="preserve">311420979</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-23</t>
+          <t xml:space="preserve">2030-02-05</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">4101367</t>
+          <t xml:space="preserve">5611242</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -13390,16 +13390,16 @@
         </is>
       </c>
       <c r="F268">
-        <v>1635</v>
+        <v>395</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418870</t>
+          <t xml:space="preserve">311421800</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-24</t>
+          <t xml:space="preserve">2030-02-10</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">5615630</t>
+          <t xml:space="preserve">5611242</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -13440,16 +13440,16 @@
         </is>
       </c>
       <c r="F269">
-        <v>1463</v>
+        <v>663</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420970</t>
+          <t xml:space="preserve">311421800</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-05</t>
+          <t xml:space="preserve">2030-02-10</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">5611242</t>
+          <t xml:space="preserve">3470126</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -13490,16 +13490,16 @@
         </is>
       </c>
       <c r="F270">
-        <v>395</v>
+        <v>633</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311421800</t>
+          <t xml:space="preserve">311422499</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-10</t>
+          <t xml:space="preserve">2030-02-13</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5611242</t>
+          <t xml:space="preserve">10108668, 100960386</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -13540,16 +13540,16 @@
         </is>
       </c>
       <c r="F271">
-        <v>663</v>
+        <v>1352</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311421800</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-10</t>
+          <t xml:space="preserve">2030-02-26</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -13581,25 +13581,25 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">3470126</t>
+          <t xml:space="preserve">10108668, 100960388</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F272">
-        <v>633</v>
+        <v>1385</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422501</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-13</t>
+          <t xml:space="preserve">2030-02-26</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -13631,20 +13631,20 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">10108668, 100960386</t>
+          <t xml:space="preserve">742672, 10108668</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F273">
-        <v>1352</v>
+        <v>280</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424645</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -13681,20 +13681,20 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">10108668, 100960388</t>
+          <t xml:space="preserve">8277101</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F274">
-        <v>1385</v>
+        <v>584</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424615</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">8277101</t>
+          <t xml:space="preserve">4090984</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -13740,16 +13740,16 @@
         </is>
       </c>
       <c r="F275">
-        <v>584</v>
+        <v>2662</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424615</t>
+          <t xml:space="preserve">311426556</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-26</t>
+          <t xml:space="preserve">2030-03-06</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">4090984</t>
+          <t xml:space="preserve">4088569</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -13790,16 +13790,16 @@
         </is>
       </c>
       <c r="F276">
-        <v>2662</v>
+        <v>313</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311426556</t>
+          <t xml:space="preserve">311427549</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-06</t>
+          <t xml:space="preserve">2030-03-12</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">4088569</t>
+          <t xml:space="preserve">4091629</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -13840,11 +13840,11 @@
         </is>
       </c>
       <c r="F277">
-        <v>313</v>
+        <v>981</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311427549</t>
+          <t xml:space="preserve">311427547</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -13881,25 +13881,25 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">4091629</t>
+          <t xml:space="preserve">4111891</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F278">
-        <v>981</v>
+        <v>611</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311427547</t>
+          <t xml:space="preserve">311430866</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-12</t>
+          <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -13931,20 +13931,20 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">4111891</t>
+          <t xml:space="preserve">7994966</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F279">
-        <v>611</v>
+        <v>944</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311430866</t>
+          <t xml:space="preserve">311430864</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -13981,20 +13981,20 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">7994966</t>
+          <t xml:space="preserve">8552609</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F280">
-        <v>944</v>
+        <v>573</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311430864</t>
+          <t xml:space="preserve">311430865</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -14031,25 +14031,25 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">8552609</t>
+          <t xml:space="preserve">4082383</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F281">
-        <v>573</v>
+        <v>370</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311430865</t>
+          <t xml:space="preserve">311432555</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-31</t>
+          <t xml:space="preserve">2030-04-14</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311441302</t>
+          <t xml:space="preserve">311441293</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311441302</t>
+          <t xml:space="preserve">311441293</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -14881,25 +14881,25 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">382839, 382840</t>
+          <t xml:space="preserve">100386913</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F298">
-        <v>2298</v>
+        <v>1303</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733943</t>
+          <t xml:space="preserve">311742070</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-18</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -14931,25 +14931,25 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">100386913</t>
+          <t xml:space="preserve">4005299</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F299">
-        <v>1303</v>
+        <v>283</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742070</t>
+          <t xml:space="preserve">311772893</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-07-11</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -14981,25 +14981,25 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">4005299</t>
+          <t xml:space="preserve">7235664</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F300">
-        <v>283</v>
+        <v>358</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311772893</t>
+          <t xml:space="preserve">311789312</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-11</t>
+          <t xml:space="preserve">2034-10-03</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">

--- a/public/exports/29189668.xlsx
+++ b/public/exports/29189668.xlsx
@@ -15894,7 +15894,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420981</t>
+          <t xml:space="preserve">311420979</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420981</t>
+          <t xml:space="preserve">311420979</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">

--- a/public/exports/29189668.xlsx
+++ b/public/exports/29189668.xlsx
@@ -3954,7 +3954,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215043</t>
+          <t xml:space="preserve">311215030</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283179</t>
+          <t xml:space="preserve">311283004</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283179</t>
+          <t xml:space="preserve">311283004</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324575</t>
+          <t xml:space="preserve">311324558</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311337037</t>
+          <t xml:space="preserve">311337033</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348100</t>
+          <t xml:space="preserve">311348107</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311362525</t>
+          <t xml:space="preserve">311362524</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">

--- a/public/exports/29189668.xlsx
+++ b/public/exports/29189668.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L327"/>
+  <dimension ref="A1:M327"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3004,10 +3249,15 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3064,10 +3314,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3124,10 +3379,15 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3184,10 +3444,15 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3244,10 +3509,15 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3304,10 +3574,15 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3364,10 +3639,15 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3424,10 +3704,15 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3484,10 +3769,15 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-01</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-01</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-18</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-16</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningstermografi</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-06-29</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-12-02</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3954,20 +4279,25 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215030</t>
+          <t xml:space="preserve">311215043</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-12</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-14</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-14</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-14</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-09</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-09</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-09</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-24</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-24</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-07</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-07</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-07</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-12</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-12</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-18</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-18</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7014,20 +7594,25 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324558</t>
+          <t xml:space="preserve">311324575</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-04</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-16</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-24</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-24</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-24</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-30</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-05</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-07</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-19</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-26</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-10</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-16</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-16</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-24</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-24</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-26</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-26</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-26</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-26</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-26</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-26</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-29</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-30</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-05</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-08</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-13</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-13</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-21</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-22</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-22</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-22</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-22</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-22</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8994,20 +9739,25 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348107</t>
+          <t xml:space="preserve">311348100</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-22</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-22</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-23</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-23</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-27</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-27</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-05</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-05</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-14</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-20</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-21</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-08</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-14</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-16</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-16</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-16</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-16</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-29</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-29</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-30</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-30</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-04</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-13</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-13</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-18</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-04</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-11</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-18</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-20</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-01</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-02</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-02</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-02</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-02</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-02</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-02</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-02</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-02</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-20</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-22</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-18</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-18</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-20</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-25</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-27</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-27</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-03</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-03</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-05</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-30</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-13</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-14</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-15</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-15</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-15</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-19</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12654,20 +13704,25 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311393677</t>
+          <t xml:space="preserve">311393687</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-19</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-21</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-29</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-29</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-29</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-29</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-29</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-03</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-03</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-03</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-05</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-05</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-17</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-23</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-26</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-26</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-26</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-30</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-30</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-30</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-30</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-01</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-03</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-08</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-08</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-29</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-29</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-05</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14334,20 +15524,25 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407500</t>
+          <t xml:space="preserve">311407501</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-15</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-22</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-22</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-22</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-22</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-22</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-25</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-04</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-09</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-10</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,15 +16244,20 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-11</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15059,15 +16309,20 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-16</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15119,15 +16374,20 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-16</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15179,15 +16439,20 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-09</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15239,15 +16504,20 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15299,15 +16569,20 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15359,15 +16634,20 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15419,15 +16699,20 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15479,15 +16764,20 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15539,15 +16829,20 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15599,15 +16894,20 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-20</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15659,15 +16959,20 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-21</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15719,15 +17024,20 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-23</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15779,15 +17089,20 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-24</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15839,15 +17154,20 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-05</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15894,20 +17214,25 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420979</t>
+          <t xml:space="preserve">311420981</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-05</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15954,20 +17279,25 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420979</t>
+          <t xml:space="preserve">311420981</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-05</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16019,15 +17349,20 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-10</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16079,15 +17414,20 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-10</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16139,15 +17479,20 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-13</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16199,15 +17544,20 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-26</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16254,20 +17604,25 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424656</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-26</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16314,20 +17669,25 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424656</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-26</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16379,15 +17739,20 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-26</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16439,15 +17804,20 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-06</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16499,15 +17869,20 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-12</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16559,15 +17934,20 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-12</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16619,15 +17999,20 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16679,15 +18064,20 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16739,15 +18129,20 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16799,15 +18194,20 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-04-14</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16859,15 +18259,20 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-04-14</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16919,15 +18324,20 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-04-14</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16979,15 +18389,20 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-04-14</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17039,15 +18454,20 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-04-20</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17099,15 +18519,20 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-01</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17159,15 +18584,20 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-01</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17219,15 +18649,20 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-01</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17279,15 +18714,20 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-29</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17339,15 +18779,20 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-03</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17399,15 +18844,20 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-03</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17459,15 +18909,20 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-01</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17519,15 +18974,20 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-26</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17579,15 +19039,20 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-16</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17639,15 +19104,20 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
+          <t xml:space="preserve">Djurs Consult ApS</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-03</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17699,15 +19169,20 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
+          <t xml:space="preserve">Djurs Consult ApS</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17759,15 +19234,20 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
+          <t xml:space="preserve">Djurs Consult ApS</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17819,15 +19299,20 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-18</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17879,15 +19364,20 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17939,15 +19429,20 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevang Tegnestue</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-11</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17999,15 +19494,20 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-03</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18059,15 +19559,20 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-17</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18119,15 +19624,20 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-05</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18179,15 +19689,20 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18239,15 +19754,20 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18299,15 +19819,20 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18359,15 +19884,20 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18419,15 +19949,20 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-08</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18479,15 +20014,20 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-08</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18539,15 +20079,20 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-09</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18599,15 +20144,20 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-09</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18659,15 +20209,20 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-09</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18719,15 +20274,20 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-09</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18779,15 +20339,20 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-09</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18839,15 +20404,20 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-09</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18899,15 +20469,20 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-09</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18959,15 +20534,20 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-09</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19019,15 +20599,20 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-09</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19079,15 +20664,20 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-12</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19139,15 +20729,20 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-12</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19199,15 +20794,20 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-12</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19259,15 +20859,20 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-19</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19319,15 +20924,20 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-19</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19379,15 +20989,20 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-19</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19439,15 +21054,20 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-19</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19499,15 +21119,20 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-19</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19559,15 +21184,20 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-19</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19619,21 +21249,26 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dantjek ApS</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L327" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L327"/>
+  <autoFilter ref="A1:M327"/>
 </worksheet>
 </file>
--- a/public/exports/29189668.xlsx
+++ b/public/exports/29189668.xlsx
@@ -4279,7 +4279,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215043</t>
+          <t xml:space="preserve">311215030</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215051</t>
+          <t xml:space="preserve">311215030</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324575</t>
+          <t xml:space="preserve">311324558</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311393687</t>
+          <t xml:space="preserve">311393677</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420981</t>
+          <t xml:space="preserve">311420979</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -17279,7 +17279,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420981</t>
+          <t xml:space="preserve">311420979</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422501</t>
+          <t xml:space="preserve">311422499</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -17604,7 +17604,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424656</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -17669,7 +17669,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424656</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -18774,12 +18774,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311441302</t>
+          <t xml:space="preserve">311441293</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -18839,12 +18839,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311441302</t>
+          <t xml:space="preserve">311441293</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K290" t="inlineStr">
